--- a/data/Oficina_de_procuradora_de_mujeres/opmVicGraf.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmVicGraf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F3D090-8815-40E0-BB4C-E4E71C14FF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC96E0D-5743-4176-917D-DEDD17FB480C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
     <t>Cantidad de víctimas (enero - diciembre 2025)</t>
   </si>
   <si>
-    <t>Cantidad de víctimas (enero - abril 2026)</t>
+    <t>Cantidad de víctimas (enero - julio 2026)</t>
   </si>
 </sst>
 </file>
@@ -107,7 +107,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -115,11 +115,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -131,6 +146,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -360,7 +378,7 @@
     <col min="9" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>6</v>
       </c>
@@ -386,7 +404,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -408,11 +426,11 @@
       <c r="G2">
         <v>1540</v>
       </c>
-      <c r="H2">
-        <v>335</v>
+      <c r="H2" s="6">
+        <v>711</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -434,11 +452,11 @@
       <c r="G3">
         <v>103</v>
       </c>
-      <c r="H3">
-        <v>15</v>
+      <c r="H3" s="6">
+        <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -460,11 +478,11 @@
       <c r="G4">
         <v>1</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -486,8 +504,8 @@
       <c r="G5">
         <v>82</v>
       </c>
-      <c r="H5">
-        <v>36</v>
+      <c r="H5" s="6">
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/data/Oficina_de_procuradora_de_mujeres/opmVicGraf.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmVicGraf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC96E0D-5743-4176-917D-DEDD17FB480C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB01938-785E-4284-A4F5-A9907BFB8312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2028" yWindow="1368" windowWidth="11424" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -427,7 +427,7 @@
         <v>1540</v>
       </c>
       <c r="H2" s="6">
-        <v>711</v>
+        <v>928</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -453,7 +453,7 @@
         <v>103</v>
       </c>
       <c r="H3" s="6">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -505,7 +505,7 @@
         <v>82</v>
       </c>
       <c r="H5" s="6">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/data/Oficina_de_procuradora_de_mujeres/opmVicGraf.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmVicGraf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB01938-785E-4284-A4F5-A9907BFB8312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB36455-0F2A-4B18-8D6C-B033FDF9DF88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2028" yWindow="1368" windowWidth="11424" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10764" yWindow="2760" windowWidth="12132" windowHeight="9384" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -427,7 +427,7 @@
         <v>1540</v>
       </c>
       <c r="H2" s="6">
-        <v>928</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -453,7 +453,7 @@
         <v>103</v>
       </c>
       <c r="H3" s="6">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -505,7 +505,7 @@
         <v>82</v>
       </c>
       <c r="H5" s="6">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
